--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.49232806654091</v>
+        <v>5.930003310812899</v>
       </c>
       <c r="D2" t="n">
-        <v>39.04999168054432</v>
+        <v>6.345623648088453</v>
       </c>
       <c r="E2" t="n">
-        <v>13.92364082968225</v>
+        <v>2.262591634823365</v>
       </c>
       <c r="F2" t="n">
-        <v>11.92225208306069</v>
+        <v>1.937365963497361</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.93956482433425</v>
+        <v>11.04017928395432</v>
       </c>
       <c r="D3" t="n">
-        <v>64.79747499623828</v>
+        <v>10.52958968688872</v>
       </c>
       <c r="E3" t="n">
-        <v>13.92364082968225</v>
+        <v>2.262591634823365</v>
       </c>
       <c r="F3" t="n">
-        <v>11.92225208306069</v>
+        <v>1.937365963497361</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.64872642309149</v>
+        <v>10.34291804375237</v>
       </c>
       <c r="D4" t="n">
-        <v>63.85816895450854</v>
+        <v>10.37695245510764</v>
       </c>
       <c r="E4" t="n">
-        <v>13.92364082968225</v>
+        <v>2.262591634823365</v>
       </c>
       <c r="F4" t="n">
-        <v>11.92225208306069</v>
+        <v>1.937365963497361</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
